--- a/resources/topic/银行从业中级风险管理_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业中级风险管理_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="Rf6e067f9815c474a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R65b1a46975bf4f6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R01f1246761a74e27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R47f7d2dd583a46c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R57c488404f864fa5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="Rbc5ef59559cd4fad"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -67955,7 +67955,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>2026-09-10 09:13:30+08:00（本地时间）</x:v>
+        <x:v>2026-09-10 15:10:54+08:00（本地时间）</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -67974,12 +67974,12 @@
         <x:v>无</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="24" hidden="0" customHeight="1">
+    <x:row r="8" ht="36" hidden="0" customHeight="1">
       <x:c r="A8" s="33" t="str">
         <x:v>说明</x:v>
       </x:c>
       <x:c r="B8" s="13" t="str">
-        <x:v>权限不足/收费题已保留行并标注；案例材料题已展开为独立题目，材料文本放在题目前。 本次对 11 道仅解析含图的题目执行 OCR，成功 3 道，失败 8 道；失败题保留图片地址并进入拒绝清单。</x:v>
+        <x:v>权限不足/收费题已保留行并标注；案例材料题已展开为独立题目，材料文本放在题目前。 复用可信 Excel 中 3 道解析图片的既有文字；仅在来源题目 ID、题干、选项和答案均一致时复用。 本次对 8 道仅解析含图的题目执行 OCR，成功 0 道，失败 8 道；失败题保留图片地址并进入拒绝清单。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/resources/topic/银行从业中级风险管理_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业中级风险管理_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R47f7d2dd583a46c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R57c488404f864fa5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="Rbc5ef59559cd4fad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R3d3efe9547904dd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R8784a357bd7f4e16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="Rd1e1235e150d43c9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -67955,7 +67955,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>2026-09-10 15:10:54+08:00（本地时间）</x:v>
+        <x:v>2026-09-12 01:05:26+08:00（本地时间）</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
